--- a/applications.xlsx
+++ b/applications.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1293,6 +1293,66 @@
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n"/>
     </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Barclays</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Sales, Trading and Structuring Analyst Discovery Programme 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Spring Week</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Sales, Trading and Structuring</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Await company response</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Application confirmation received from Barclays Workday system. Job reference: JR-0000082018.</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>19d0b2fd92dad3eb</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/applications.xlsx
+++ b/applications.xlsx
@@ -1351,7 +1351,7 @@
           <t>19d0b2fd92dad3eb</t>
         </is>
       </c>
-      <c r="N16" s="6" t="inlineStr"/>
+      <c r="N16" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
